--- a/presentations/heatmap_byhand/xlsx/baseline_methods/nist_sp_800_30/risk_ranking_slackMCP_nist800_30.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/nist_sp_800_30/risk_ranking_slackMCP_nist800_30.xlsx
@@ -653,12 +653,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -677,6 +678,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -692,6 +698,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=Critical (private channel PII); max → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -707,6 +718,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=Critical (private thread content); max → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -722,6 +738,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=Critical (direct PII asset); max → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -737,6 +758,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=High (social engineering; post_message overrides to High); max → High</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -752,6 +778,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=High (phishing reply; Impact adjusted to High); max → High</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -767,6 +798,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=Critical (bulk PII enumeration); max → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -782,6 +818,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Likelihood=High; Impact=Medium (channel-name recon only); max → High</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -795,6 +836,11 @@
       <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Likelihood=Low; Impact=Low (emoji reaction, minimal); max → Low</t>
         </is>
       </c>
     </row>
@@ -809,12 +855,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -833,6 +880,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -848,6 +900,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Channel sensitivity=Critical; read tools Likelihood=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -863,6 +920,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Channel sensitivity=Critical; PII-heavy; read Likelihood=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -878,6 +940,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Channel sensitivity=Low; write Likelihood=High; max(High,Low) = Low</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -893,6 +960,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Channel sensitivity=High; read Likelihood=High → High</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -906,6 +978,11 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Channel sensitivity=High; read Likelihood=High → High</t>
         </is>
       </c>
     </row>
@@ -935,12 +1012,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -959,6 +1037,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -974,6 +1057,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Asset Impact=Critical; read Likelihood=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -989,6 +1077,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Asset Impact=Critical; read Likelihood=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -1004,6 +1097,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Asset Impact=Medium; read Likelihood=High → High</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -1017,6 +1115,11 @@
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Asset Impact=Medium; read Likelihood=High → High</t>
         </is>
       </c>
     </row>
